--- a/www/download/COUNTRY.BRA.rpO1.xlsx
+++ b/www/download/COUNTRY.BRA.rpO1.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Brasil</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>0.915734113517542</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>1.00469193759665</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>1.0775397229446</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>1.15970262026583</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>1.80401219237676</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>1.82715152306013</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>2.33426698569532</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>2.82845434464621</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>3.05819743146939</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>2.92039006162992</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>2.42365480933938</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>2.17533179323684</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.252</t>
+          <t>1.94704053129045</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>1.83376551466426</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.296</t>
+          <t>1.99942819729204</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>73.545</t>
+          <t>1.06248015327343</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>71.986</t>
+          <t>1.01545903352748</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>73.128</t>
+          <t>0.967445368778669</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>72.745</t>
+          <t>0.9827529203729</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>76.641</t>
+          <t>1.06658858840686</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>78.972</t>
+          <t>1.023499745318</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>79.544</t>
+          <t>0.978094657981355</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>82.629</t>
+          <t>1.01933583207463</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>84.035</t>
+          <t>1.10073199490121</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>88.252</t>
+          <t>1.0603160880001</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>90.906</t>
+          <t>1.10629975810837</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>93.247</t>
+          <t>1.14017930396556</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>94.714</t>
+          <t>1.16126228139957</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>96.233</t>
+          <t>1.16761821325767</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>96.647</t>
+          <t>1.17684793010923</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>59.052</t>
+          <t>3.76728950720739</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>57.777</t>
+          <t>3.70182367167653</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>58.432</t>
+          <t>3.64327924230533</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>57.853</t>
+          <t>3.70853562239997</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>60.702</t>
+          <t>3.95714176307784</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>62.692</t>
+          <t>3.852824118362</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>63.064</t>
+          <t>3.79819552047183</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>65.474</t>
+          <t>3.95640974048312</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>66.734</t>
+          <t>4.13422162478796</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>70.286</t>
+          <t>4.01767058544832</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>72.221</t>
+          <t>4.0949654431143</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>73.868</t>
+          <t>4.05312964319434</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>74.771</t>
+          <t>4.00364137424641</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>75.799</t>
+          <t>3.92110928272434</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>76.071</t>
+          <t>3.85925619262483</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>157522.872</t>
+          <t>6.30626924312538</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>154975.268</t>
+          <t>6.09392366109493</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>158449.89</t>
+          <t>5.9119080919902</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>158213.64</t>
+          <t>5.88058080856142</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>164642.11</t>
+          <t>6.10656062273012</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>170373.593</t>
+          <t>5.86793945936931</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>172038.194</t>
+          <t>5.69977242116771</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>179030.577</t>
+          <t>5.80610489223123</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>181564.871</t>
+          <t>5.91319139038006</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>189442.152</t>
+          <t>5.62416823438461</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>193103.106</t>
+          <t>5.60427711573707</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>197824.902</t>
+          <t>5.46648260985424</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>201071.541</t>
+          <t>5.30923432744783</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>204334.615</t>
+          <t>5.10709294328622</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>205284.27</t>
+          <t>4.91947910642274</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>124855.477</t>
+          <t>24179638904178</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>122981.929</t>
+          <t>23624925651529.1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>125000.246</t>
+          <t>24796639940830.4</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>124217.313</t>
+          <t>26841983106506.4</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>128568.971</t>
+          <t>19950777031738.5</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>133539.152</t>
+          <t>26840146372245.8</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>134738.042</t>
+          <t>24851913447990.1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>140161.944</t>
+          <t>22067089625869.1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>142510.189</t>
+          <t>22855527345276.7</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>149104.054</t>
+          <t>23300759862716.2</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>151507.858</t>
+          <t>27597614637785.9</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>154756.786</t>
+          <t>28484944601259.8</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>156829.399</t>
+          <t>30747501717255.3</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>159080.283</t>
+          <t>28385658934862.6</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>159733.056</t>
+          <t>26893736832383.7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>5885499047264.33</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>28.91</t>
+          <t>5747683425476.97</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>29.29</t>
+          <t>5945861682224.38</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>29.66</t>
+          <t>6502112235336.28</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>30.04</t>
+          <t>4747740589294.4</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>30.42</t>
+          <t>5777201931232.76</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>5347184516245.87</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>31.18</t>
+          <t>4729967269467.2</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>4740479687492.6</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>31.41</t>
+          <t>4660167068447.37</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>31.52</t>
+          <t>5633113305632.8</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>31.97</t>
+          <t>6048846081952.43</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>32.43</t>
+          <t>5740414411917.62</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>32.88</t>
+          <t>5251999031858.24</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>33.34</t>
+          <t>5216380579671.79</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>30.28</t>
+          <t>759540633.083698</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>30.81</t>
+          <t>702912780.638657</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>31.33</t>
+          <t>711161434.107904</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>811400157.093242</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>32.38</t>
+          <t>845114008.026763</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>966101650.157224</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>33.42</t>
+          <t>1031988526.79857</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>33.95</t>
+          <t>960950189.405773</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>34.78</t>
+          <t>901534352.871002</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>35.61</t>
+          <t>752035503.461284</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>36.44</t>
+          <t>696046777.749608</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>37.03</t>
+          <t>603906365.198655</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>37.63</t>
+          <t>529489214.704007</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>38.22</t>
+          <t>397555532.911707</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>38.81</t>
+          <t>411692319.575089</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>38.33</t>
+          <t>624192.679604979</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>37.43</t>
+          <t>687248.390815925</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>36.53</t>
+          <t>708692.570470619</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>35.62</t>
+          <t>703072.278506279</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>34.72</t>
+          <t>480878.834117722</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>33.82</t>
+          <t>550804.005504075</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>32.92</t>
+          <t>469787.736084133</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>32.01</t>
+          <t>436418.205489388</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>31.07</t>
+          <t>465876.94822259</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>567016.255057347</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>29.18</t>
+          <t>763281.219820082</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>28.14</t>
+          <t>943053.006129781</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>27.09</t>
+          <t>1399094.97454209</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>26.04</t>
+          <t>1705011.41132126</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>1745960.02150987</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>1087036.34956857</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>11.22</t>
+          <t>1192957.98475986</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>11.43</t>
+          <t>1225820.80847727</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>11.63</t>
+          <t>1204203.6511635</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>11.83</t>
+          <t>834311.617919726</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>12.04</t>
+          <t>989669.241823144</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>12.24</t>
+          <t>866496.779308652</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>12.44</t>
+          <t>804428.220042839</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>12.78</t>
+          <t>875427.061052626</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>13.12</t>
+          <t>1072686.66761498</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>1422173.11685508</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>1702727.90277668</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>2451091.98378094</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>15.71</t>
+          <t>3014779.59326862</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>16.46</t>
+          <t>2973757.44356738</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>27.36</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>3.34948286612086</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>30.88</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>32.05</t>
+          <t>3.34712982951139</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>33.23</t>
+          <t>3.26195613203209</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>34.4</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>35.57</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>37.02</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>38.47</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>39.92</t>
+          <t>3.22717304870096</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>41.03</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>42.15</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>43.26</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>44.38</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>58.76</t>
+          <t>176456.739795647</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>57.39</t>
+          <t>171881.591541854</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>56.01</t>
+          <t>171384.406107029</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>54.63</t>
+          <t>160891.712033725</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>53.26</t>
+          <t>113760.958790005</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>51.88</t>
+          <t>131607.250077569</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>118662.525337633</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>49.13</t>
+          <t>112217.792776431</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>47.34</t>
+          <t>120483.288061918</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>45.56</t>
+          <t>141621.64922617</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>43.77</t>
+          <t>179120.441546385</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>41.91</t>
+          <t>204740.203811757</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>40.04</t>
+          <t>252043.150529306</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>38.18</t>
+          <t>314590.733405019</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>36.31</t>
+          <t>296158.785803693</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.915734113517542</t>
+          <t>99666.5566087935</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.00469193759665</t>
+          <t>99480.4254602614</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.0775397229446</t>
+          <t>101757.302832335</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1.15970262026583</t>
+          <t>112389.746527187</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.80401219237676</t>
+          <t>78214.2283217795</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.82715152306013</t>
+          <t>92152.6198589365</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.33426698569532</t>
+          <t>84789.2158924162</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2.82845434464621</t>
+          <t>72241.77850323</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>3.05819743146939</t>
+          <t>71035.8066849005</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2.92039006162992</t>
+          <t>66302.9582400855</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2.42365480933938</t>
+          <t>77997.7429362036</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2.17533179323684</t>
+          <t>81887.0967904073</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>1.94704053129045</t>
+          <t>76773.3165469867</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>1.83376551466426</t>
+          <t>69288.3741180356</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1.99942819729204</t>
+          <t>68572.781812614</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.328</t>
+          <t>97517615721.5769</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>-10527441492.2611</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>-1230986300.18483</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.354</t>
+          <t>-54827355845.3378</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.243</t>
+          <t>95208874541.4288</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.261</t>
+          <t>79816844769.2844</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>184497022783.867</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.208</t>
+          <t>443689263097.855</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>506669639365.636</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.261</t>
+          <t>574156278108.559</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.355</t>
+          <t>520922820673.489</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.446</t>
+          <t>572532358936.755</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.565</t>
+          <t>8974051478.1217</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.691</t>
+          <t>125729131109.869</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.707</t>
+          <t>-233685890579.184</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>210133039358.626</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.386</t>
+          <t>102553413381.866</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.383</t>
+          <t>125540752300.074</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.374</t>
+          <t>82963717820.1704</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.256</t>
+          <t>191265658123.235</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>265671840809.535</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>398254017300.699</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>561221062444.175</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>624603692768.264</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.275</t>
+          <t>637063116557.087</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>662120665854.727</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.473</t>
+          <t>705084837652.932</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.695</t>
+          <t>132956497979.711</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.837</t>
+          <t>248104615506.354</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.847</t>
+          <t>-42888747033.7876</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2.658</t>
+          <t>-112615423637.049</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2.755</t>
+          <t>-113080854874.127</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2.787</t>
+          <t>-126771738600.259</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2.719</t>
+          <t>-137791073665.508</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.895</t>
+          <t>-96056783581.8063</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2.116</t>
+          <t>-185854996040.25</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.834</t>
+          <t>-213756994516.832</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.768</t>
+          <t>-117531799346.32</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1.809</t>
+          <t>-117934053402.628</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2.085</t>
+          <t>-62906838448.5282</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2.611</t>
+          <t>-141197845181.238</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2.933</t>
+          <t>-132552478716.177</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>3.543</t>
+          <t>-123982446501.589</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>4.244</t>
+          <t>-122375484396.484</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>4.228</t>
+          <t>-190797143545.396</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.262</t>
+          <t>446753.111357039</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.366</t>
+          <t>432688.40605382</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.421</t>
+          <t>431174.021348664</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>473663.01512614</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>340007.405029823</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1.097</t>
+          <t>392750.423290616</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.948</t>
+          <t>351641.1621564</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.898</t>
+          <t>303858.4526728</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.979</t>
+          <t>307162.37312434</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1.175</t>
+          <t>278387.60439534</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1.562</t>
+          <t>329709.956799426</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>1.895</t>
+          <t>339222.264863927</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2.377</t>
+          <t>310970.257587668</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2.895</t>
+          <t>273672.101149848</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2.741</t>
+          <t>265145.67698269</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.673</t>
+          <t>396013.497937715</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.739</t>
+          <t>396080.968828338</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.771</t>
+          <t>406363.470977529</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.747</t>
+          <t>450280.494282955</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.514</t>
+          <t>317777.504401535</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.559</t>
+          <t>388495.243862528</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.479</t>
+          <t>357061.2851421</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>305247.624051274</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.481</t>
+          <t>301122.572080186</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>285533.311127174</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>339222.634814837</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.935</t>
+          <t>360254.202562434</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>1.175</t>
+          <t>391912.766929523</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>1.407</t>
+          <t>348374.878969464</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1.398</t>
+          <t>343707.2307199</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>106.25</t>
+          <t>55919.0744709033</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>101.55</t>
+          <t>55162.1956404715</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>96.74</t>
+          <t>59446.5520192967</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>98.28</t>
+          <t>58540.8818546665</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>106.66</t>
+          <t>55558.9445026074</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>102.35</t>
+          <t>64412.2788355735</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>97.81</t>
+          <t>67952.387212892</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>101.93</t>
+          <t>73652.5956675123</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>110.07</t>
+          <t>83307.2466443061</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>106.03</t>
+          <t>109195.004740986</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>110.63</t>
+          <t>134029.798305241</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>114.02</t>
+          <t>156508.079884294</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>116.13</t>
+          <t>182673.133968401</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>116.76</t>
+          <t>225925.787330055</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>117.68</t>
+          <t>177168.145813593</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>376.73</t>
+          <t>1498796942941.21</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>370.18</t>
+          <t>1381058126843.57</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>364.33</t>
+          <t>1531993854944.12</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>370.85</t>
+          <t>1735469982453.98</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>395.71</t>
+          <t>1699998674031.83</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>385.28</t>
+          <t>2267186420860.09</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>379.82</t>
+          <t>2537022368540.33</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>395.64</t>
+          <t>2521193126101.49</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>413.42</t>
+          <t>2666118351489.39</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>401.77</t>
+          <t>2947386147183.35</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>409.5</t>
+          <t>3273858115897.06</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>405.31</t>
+          <t>3231295828516.96</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>400.36</t>
+          <t>3244242919304.68</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>392.11</t>
+          <t>2865402355194.45</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>385.93</t>
+          <t>2354404950155.52</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>630.63</t>
+          <t>63624.5740749555</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>609.39</t>
+          <t>66099.9739901101</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>591.19</t>
+          <t>73317.6085475123</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>588.06</t>
+          <t>70462.4594564374</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>610.66</t>
+          <t>60009.8886529971</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>586.79</t>
+          <t>71432.036347915</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>569.98</t>
+          <t>71207.593913016</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>580.61</t>
+          <t>62298.8280490103</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>591.32</t>
+          <t>63637.2100849141</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>562.42</t>
+          <t>79039.9726229725</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>560.43</t>
+          <t>96807.0042247079</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>546.65</t>
+          <t>118387.998731804</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>530.92</t>
+          <t>153431.634813008</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>510.71</t>
+          <t>211376.023931242</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>491.95</t>
+          <t>168974.33912302</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>29124900.468</t>
+          <t>1877541746303.14</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>28512144.172</t>
+          <t>1726498433975.85</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>29716643.829</t>
+          <t>1993163397032.86</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>32755591.894</t>
+          <t>2127717348268.6</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>24354788.347</t>
+          <t>1974924194008.31</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>30680381.206</t>
+          <t>2666426389385.72</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>28402230.689</t>
+          <t>2880804853557.68</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>25222326.379</t>
+          <t>2429265762318.68</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>25304829.623</t>
+          <t>2298719014169.17</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>25199020.831</t>
+          <t>2422406365424.03</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>30837261.915</t>
+          <t>2588620556756.63</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>33592610.297</t>
+          <t>2750722406684.25</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>37119590.143</t>
+          <t>2658427449559.34</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>33525023.513</t>
+          <t>2772381917722.62</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>33218320.503</t>
+          <t>1999501372056.69</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>26381617.874</t>
+          <t>-7705.49960405221</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>24999450.579</t>
+          <t>-10937.7783496386</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>25194271.276</t>
+          <t>-13871.0565282157</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>27402945.386</t>
+          <t>-11921.5776017709</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20639044.739</t>
+          <t>-4450.94415038973</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>24622181.197</t>
+          <t>-7019.75751234143</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>22176053.379</t>
+          <t>-3255.20670012402</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>19894866.454</t>
+          <t>11353.7676185021</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>20498070.741</t>
+          <t>19670.036559392</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>19566740.017</t>
+          <t>30155.0321180136</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>23812144.746</t>
+          <t>37222.794080533</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>25057711.754</t>
+          <t>38120.0811524903</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>23251544.008</t>
+          <t>29241.4991553926</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>20744109.363</t>
+          <t>14549.7633988127</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>20169821.373</t>
+          <t>8193.80669057303</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>24179638.904</t>
+          <t>-378744803361.932</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>23624925.652</t>
+          <t>-345440307132.288</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>24796639.941</t>
+          <t>-461169542088.74</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>26841983.107</t>
+          <t>-392247365814.623</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>19950777.032</t>
+          <t>-274925519976.479</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>26840146.372</t>
+          <t>-399239968525.633</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>24851913.448</t>
+          <t>-343782485017.347</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>22067089.626</t>
+          <t>91927363782.8069</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>22855527.345</t>
+          <t>367399337320.212</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>23300759.863</t>
+          <t>524979781759.315</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>27597614.638</t>
+          <t>685237559140.423</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>28484944.601</t>
+          <t>480573421832.707</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>30747501.717</t>
+          <t>585815469745.338</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>28385658.935</t>
+          <t>93020437471.8328</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>26893736.832</t>
+          <t>354903578098.83</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1.087</t>
+          <t>307826.44203</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.193</t>
+          <t>325696.19641</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.226</t>
+          <t>339814.34862</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1.204</t>
+          <t>325817.53526</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.834</t>
+          <t>226786.80764</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>258213.76393</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.866</t>
+          <t>218486.14965</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.804</t>
+          <t>207952.31113</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.875</t>
+          <t>227846.57867</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1.073</t>
+          <t>277971.10007</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>1.422</t>
+          <t>354224.1177</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>1.703</t>
+          <t>431003.88651</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>2.451</t>
+          <t>534472.07806</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>3.015</t>
+          <t>649810.03032</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2.974</t>
+          <t>630373.14299</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>13884313.625</t>
+          <t>0.052243997889939</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>13610028.471</t>
+          <t>0.065799993055667</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>14335859.187</t>
+          <t>0.0776988822262481</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>15671646.739</t>
+          <t>0.0778435962654476</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>11499188.304</t>
+          <t>0.0763542861746593</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>14937980.797</t>
+          <t>0.0704698143911199</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>13473938.317</t>
+          <t>0.0658454504105279</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>11971832.185</t>
+          <t>0.0661604297998362</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>12163050.245</t>
+          <t>0.0710038395042892</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>12316653.125</t>
+          <t>0.0740190724686711</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>14811657.396</t>
+          <t>0.0789540182471218</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>15776339.01</t>
+          <t>0.087638324913398</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>17550820.376</t>
+          <t>0.0643661972494932</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>16053535.89</t>
+          <t>0.060265930537589</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>15789919.06</t>
+          <t>0.0602964293712051</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.624</t>
+          <t>328022.217561222</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.687</t>
+          <t>357050.860492582</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.709</t>
+          <t>359800.07234588</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.703</t>
+          <t>354405.445036471</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.481</t>
+          <t>243070.117973706</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.551</t>
+          <t>261244.890042264</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>226361.85432922</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.436</t>
+          <t>208054.975411469</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.466</t>
+          <t>219695.42882029</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.567</t>
+          <t>261347.622060217</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.763</t>
+          <t>355201.572591124</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.943</t>
+          <t>445629.031897406</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>1.399</t>
+          <t>564910.169945729</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>1.705</t>
+          <t>691295.03710285</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>1.746</t>
+          <t>706701.547310895</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>5885499.047</t>
+          <t>357464.215007532</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>5747683.425</t>
+          <t>386261.837240327</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>5945861.682</t>
+          <t>382909.754649366</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>6502112.235</t>
+          <t>374196.607393886</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>4747740.589</t>
+          <t>255838.859720888</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>5777201.931</t>
+          <t>278432.354738735</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>5347184.516</t>
+          <t>239810.05324894</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>4729967.269</t>
+          <t>220899.745023004</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>4740479.687</t>
+          <t>231929.903542001</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>4660167.068</t>
+          <t>274582.276132272</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>5633113.306</t>
+          <t>374878.242364804</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>6048846.082</t>
+          <t>473406.172577666</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>5740414.412</t>
+          <t>694954.107433865</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>5251999.032</t>
+          <t>836641.718047541</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>5216380.58</t>
+          <t>846505.046696694</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>2657544.91490704</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>2754537.28489732</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>2787196.46883731</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>2718929.34610389</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>1895367.49971133</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>2115917.71359179</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>1833706.71262236</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>1768386.41775049</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>1809238.63981075</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>2085356.56153879</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>2610569.13966916</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>2933384.85080145</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>3542955.74900728</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>4243999.76630099</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>4227866.28044271</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>759.541</t>
+          <t>357464.215007532</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>702.913</t>
+          <t>368611.060278216</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>711.161</t>
+          <t>367759.103557952</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>811.4</t>
+          <t>377762.247685968</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>845.114</t>
+          <t>371747.508532344</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>966.102</t>
+          <t>394993.174258897</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1031.989</t>
+          <t>395005.131467663</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>960.95</t>
+          <t>398454.12120389</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>901.534</t>
+          <t>399955.482576774</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>752.036</t>
+          <t>420381.380490107</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>696.047</t>
+          <t>441348.130864091</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>603.906</t>
+          <t>463664.07274651</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>529.489</t>
+          <t>570469.744645256</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>397.556</t>
+          <t>598485.341610338</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>411.692</t>
+          <t>596660.920536902</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>328022.217561222</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>339770.95492785</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>344721.618845927</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>357115.059466346</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>352424.195876436</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>371020.318605678</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>372873.535863077</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>375221.962253843</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>378721.31730579</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>400969.203275503</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>418931.130914099</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>437298.196131812</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>461894.667202679</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>492391.934259925</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>496391.703197306</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>315297.510722468</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>353130.125759673</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>387946.456280634</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>372542.950326114</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>258480.391269112</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>280715.578621265</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>239403.76975106</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>229214.998226996</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>248946.178067999</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>295977.807677728</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>385235.365035196</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>461817.138462334</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>480089.739116135</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>570359.328522459</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>551084.026373306</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>26381617873835.9</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>24999450578998.9</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>25194271276350.8</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>27402945386418.7</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>20639044738503.7</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>24622181196805.1</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>22176053378571</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>19894866453613.5</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>20498070740815.1</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>19566740017382.4</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>23812144745849.8</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>25057711753844.6</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>23251544008021</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>20744109362951.3</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>20169821372800.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>29124900467845.6</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>28512144172205</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>29716643828547</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>32755591894338.9</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>24354788347240</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>30680381206161.2</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>28402230688715.2</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>25222326379323.5</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>25304829623429.6</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>25199020830851.5</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>30837261914676</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>33592610296933.8</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>37119590142901</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>33525023513290.7</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>33218320502691.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>13884313625270.9</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>13610028470891.7</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>14335859186899.5</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>15671646738560</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>11499188304109.3</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>14937980797417.3</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>13473938316776.3</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>11971832184582.5</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>12163050245250.9</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>12316653125486.7</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>14811657396137</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>15776339009804.5</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>17550820375976.9</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>16053535890277.5</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>15789919060117</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>73545221.6136996</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>71985645.4011104</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>73128236.0519808</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>72744860.8372439</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>76641008.2837895</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>78972347</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>79544414</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>82629067</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>84034981</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>88252473</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>90905673</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>93246963</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>94713909</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>96232609</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>96647139</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>59051895.1142841</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>57777028.9872046</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>58431793.2642276</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>57853251.1750386</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>60701750.7065571</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>62691673.2272644</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>63064441.1552358</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>65474125.4640584</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>66733664.4534825</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>70285959.9653567</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>72221491.2069989</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>73868122.3176669</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>74770957.8028244</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>75799138.0041801</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>76070715.5490115</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>157522871815.931</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>154975267826.828</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>158449890428.51</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>158213639601.25</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>164642110208.336</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>170373593179.634</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>172038193512.572</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>179030577348.644</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>181564871488.186</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>189442152116.396</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>193103105662.399</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>197824901761.945</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>201071540982.591</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>204334614712.513</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>205284270174.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>124855477356.272</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>122981929130.877</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>125000245608.597</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>124217313012.641</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>128568970516.355</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>133539151699.074</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>134738041576.624</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>140161944231.357</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>142510188701.274</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>149104053980.659</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>151507858121.156</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>154756786038.698</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>156829398560.943</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>159080283416.758</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>159733056266.715</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.28527207953238</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.289063672026907</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.292855264521435</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.296646857015962</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.30043844951049</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.304230042005017</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.308021634499545</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.311813226994072</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.312940804118395</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.314068381242717</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.31519595836704</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.319739582810603</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.324283207254166</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.32882683169773</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.333370456141293</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.302847446399263</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.308080715976869</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.313313985554475</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.318547255132081</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.323780524709687</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.329013794287293</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.334247063864899</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.339480333442505</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.347788509864734</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.356096686286962</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.36440486270919</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.370335501013448</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.376266139317706</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.382196777621964</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.388127415926222</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.383309045496929</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.374284183424795</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.365259321352662</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.356234459280528</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.347209597208395</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.338184735136261</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.329159873064128</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.320135010991994</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.310699257445443</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.301263503898892</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.291827750352342</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.28135348760452</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.270879224856699</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.260404962108878</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.249930699361057</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.110215680880114</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.112243117090419</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.114270553300723</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.116297989511028</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.118325425721333</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.120352861931638</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.122380298141942</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.124407734352247</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.127782000052277</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.131156265752308</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.134530531452338</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.142041661732327</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.149552792012316</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.157063922292304</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.164575052572293</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.273601964623949</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.285335237123337</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.297068509622725</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.308801782122114</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.320535054621502</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.33226832712089</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.344001599620279</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.355734872119667</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.370214731055326</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.384694589990986</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.399174448926646</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.41032044478257</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.421466440638494</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.432612436494418</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.443758432350343</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.587610925924509</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.573850217214816</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.560089508505123</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.54632879979543</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.532568091085737</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.518807382376044</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.50504667366635</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.491285964956657</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.473431840320967</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.455577715685277</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.437723591049587</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.419066464913674</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.400409338777762</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.381752212641849</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.363095086505936</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1261526.44119</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1366247.23366</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1420617.91803</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>1380365.38991</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>969896.04007</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>1096554.37795</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>948116.04885</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>897641.136</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>978595.75461</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>1175437.15757</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>1562385.44245</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>1895074.57938</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>2377320.84208</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>2894929.56407</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>2741154.20109</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>672761.72573</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>739391.963</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>770856.21093</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>746739.55772</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>514319.25099</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>559147.93336</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>479213.823</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>450114.74325</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>480876.08161</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>570560.08381</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>760113.6074</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>935223.31104</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>1175043.84655</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>1407001.04657</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>1397589.07307</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2433604.55329256</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2496405.24300983</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2573259.57977903</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2650481.85683378</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2717570.77314825</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>2799141.45096697</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2886846.91913392</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>2963511.49594946</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>3029294.64737244</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>3121399.53784588</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>3243195.30579049</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>3429017.52373446</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>3675487.88361005</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>3959516.16837724</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>4181401.4404286</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO1</t>
